--- a/data/2023-24/ICEHLdelegacije.xlsx
+++ b/data/2023-24/ICEHLdelegacije.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561B8403-FC79-4BAB-A0F2-F1B2C51C37FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="ICEHL" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="ICEHL_DAT" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="ICEHL_DAT_STRING" state="visible" r:id="rId6"/>
+    <sheet name="ICEHL" sheetId="1" r:id="rId1"/>
+    <sheet name="ICEHL_DAT" sheetId="3" r:id="rId2"/>
+    <sheet name="ICEHL_DAT_STRING" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1539,14 +1553,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1587,15 +1601,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1870,9 +1907,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:BC134"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:BB134"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1931,225 +1968,225 @@
     <col min="58" max="58" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.45" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:54" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>COUNTIF(A4:A70,"&lt;&gt;")</f>
+        <f t="shared" ref="A2:AF2" si="0">COUNTIF(A4:A70,"&lt;&gt;")</f>
         <v>57</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(B4:B70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="C2">
-        <f>COUNTIF(C4:C70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="D2">
-        <f>COUNTIF(D4:D70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="E2">
-        <f>COUNTIF(E4:E70,"&lt;&gt;")</f>
-        <v>52</v>
+        <f t="shared" si="0"/>
+        <v>53</v>
       </c>
       <c r="F2">
-        <f>COUNTIF(F4:F70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="G2">
-        <f>COUNTIF(G4:G70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="H2">
-        <f>COUNTIF(H4:H70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="I2">
-        <f>COUNTIF(I4:I70,"&lt;&gt;")</f>
+      <c r="J2">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="J2">
-        <f>COUNTIF(J4:J70,"&lt;&gt;")</f>
-        <v>39</v>
-      </c>
       <c r="K2">
-        <f>COUNTIF(K4:K70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="L2">
-        <f>COUNTIF(L4:L70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="M2">
-        <f>COUNTIF(M4:M70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="N2">
-        <f>COUNTIF(N4:N70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="O2">
-        <f>COUNTIF(O4:O70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="P2">
-        <f>COUNTIF(P4:P70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="Q2">
-        <f>COUNTIF(Q4:Q70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="R2">
-        <f>COUNTIF(R4:R70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="S2">
-        <f>COUNTIF(S4:S70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="T2">
-        <f>COUNTIF(T4:T70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="U2">
-        <f>COUNTIF(U4:U70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="V2">
-        <f>COUNTIF(V4:V70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="W2">
-        <f>COUNTIF(W4:W70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="X2">
-        <f>COUNTIF(X4:X70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="Y2">
-        <f>COUNTIF(Y4:Y70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="Z2">
-        <f>COUNTIF(Z4:Z70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="AA2">
-        <f>COUNTIF(AA4:AA70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="AB2">
-        <f>COUNTIF(AB4:AB70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="AC2">
-        <f>COUNTIF(AC4:AC70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="AD2">
-        <f>COUNTIF(AD4:AD70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="AE2">
-        <f>COUNTIF(AE4:AE70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AF2">
-        <f>COUNTIF(AF4:AF70,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="AG2">
-        <f>COUNTIF(AG4:AG70,"&lt;&gt;")</f>
+        <f t="shared" ref="AG2:BB2" si="1">COUNTIF(AG4:AG70,"&lt;&gt;")</f>
         <v>22</v>
       </c>
       <c r="AH2">
-        <f>COUNTIF(AH4:AH70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="AI2">
-        <f>COUNTIF(AI4:AI70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="AJ2">
-        <f>COUNTIF(AJ4:AJ70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AK2">
-        <f>COUNTIF(AK4:AK70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AL2">
-        <f>COUNTIF(AL4:AL70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="AM2">
-        <f>COUNTIF(AM4:AM70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AN2">
-        <f>COUNTIF(AN4:AN70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="AO2">
-        <f>COUNTIF(AO4:AO70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="AP2">
-        <f>COUNTIF(AP4:AP70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AQ2">
-        <f>COUNTIF(AQ4:AQ70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="AR2">
-        <f>COUNTIF(AR4:AR70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="AS2">
-        <f>COUNTIF(AS4:AS70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="AT2">
-        <f>COUNTIF(AT4:AT70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AU2">
-        <f>COUNTIF(AU4:AU70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AV2">
-        <f>COUNTIF(AV4:AV70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="AW2">
-        <f>COUNTIF(AW4:AW70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="AX2">
-        <f>COUNTIF(AX4:AX70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="AY2">
-        <f>COUNTIF(AY4:AY70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="AZ2">
-        <f>COUNTIF(AZ4:AZ70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="BA2">
-        <f>COUNTIF(BA4:BA70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BB2">
-        <f>COUNTIF(BB4:BB70,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2313,7 +2350,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -2477,7 +2514,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -2635,7 +2672,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -2790,7 +2827,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -2945,7 +2982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -3100,7 +3137,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -3249,7 +3286,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -3395,7 +3432,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -3541,7 +3578,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3684,7 +3721,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -3821,7 +3858,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -3954,9 +3991,8 @@
       <c r="AR14" t="s">
         <v>113</v>
       </c>
-      <c r="AS14" s="1"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -4090,7 +4126,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>86</v>
       </c>
@@ -4221,7 +4257,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -4352,7 +4388,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -4480,7 +4516,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
@@ -4605,7 +4641,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -4727,7 +4763,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -4849,7 +4885,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>96</v>
       </c>
@@ -4965,7 +5001,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -5072,7 +5108,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>114</v>
       </c>
@@ -5177,7 +5213,7 @@
       </c>
       <c r="AM24" s="2"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -5278,7 +5314,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -5371,7 +5407,7 @@
       </c>
       <c r="AJ26" s="2"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -5464,7 +5500,7 @@
       </c>
       <c r="AG27" s="2"/>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -5553,7 +5589,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>104</v>
       </c>
@@ -5641,7 +5677,7 @@
       <c r="AH29" s="2"/>
       <c r="AO29" s="2"/>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -5727,7 +5763,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -5813,7 +5849,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>109</v>
       </c>
@@ -5893,7 +5929,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>119</v>
       </c>
@@ -5921,7 +5957,7 @@
       <c r="I33" t="s">
         <v>134</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K33" t="s">
@@ -5961,7 +5997,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -6030,7 +6066,7 @@
       </c>
       <c r="Y34" s="2"/>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -6092,7 +6128,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -6152,7 +6188,7 @@
       </c>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -6211,7 +6247,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -6255,7 +6291,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -6296,7 +6332,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -6334,7 +6370,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -6367,7 +6403,7 @@
       </c>
       <c r="AI41" s="2"/>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>117</v>
       </c>
@@ -6399,7 +6435,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>88</v>
       </c>
@@ -6431,7 +6467,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>105</v>
       </c>
@@ -6460,7 +6496,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>110</v>
       </c>
@@ -6483,7 +6519,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -6503,7 +6539,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>124</v>
       </c>
@@ -6523,7 +6559,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>125</v>
       </c>
@@ -6543,7 +6579,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -6563,7 +6599,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>129</v>
       </c>
@@ -6583,7 +6619,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>132</v>
       </c>
@@ -6603,7 +6639,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -6623,7 +6659,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>134</v>
       </c>
@@ -6640,7 +6676,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>135</v>
       </c>
@@ -6657,7 +6693,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>142</v>
       </c>
@@ -6674,7 +6710,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>138</v>
       </c>
@@ -6688,30 +6724,30 @@
         <v>152</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6783,15 +6819,25 @@
     <row r="133" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="134" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="M32">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>A4 &gt; "2024-02-24"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:XFD62">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>A4&gt; "2024-02-24"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:CU42"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -6825,7 +6871,7 @@
     <col min="100" max="100" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -7124,7 +7170,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -7423,7 +7469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -7722,7 +7768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -8021,7 +8067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -8320,7 +8366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -8538,7 +8584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:89" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -8756,7 +8802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:89" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -8974,7 +9020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:89" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -9192,7 +9238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -9377,7 +9423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -9562,7 +9608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -9747,7 +9793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -9932,7 +9978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -10084,7 +10130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -10236,7 +10282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -10388,7 +10434,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -10540,7 +10586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -10665,7 +10711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -10790,7 +10836,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -10915,7 +10961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -11040,7 +11086,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -11141,7 +11187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -11242,7 +11288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -11343,7 +11389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -11444,11 +11490,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11464,10 +11510,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:CU1898"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -11552,7 +11598,7 @@
     <col min="101" max="101" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -11851,7 +11897,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -12150,7 +12196,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:99" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>249</v>
       </c>
@@ -12371,7 +12417,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>317</v>
       </c>
@@ -12559,7 +12605,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>375</v>
       </c>
@@ -12717,7 +12763,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>424</v>
       </c>
@@ -12845,7 +12891,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>461</v>
       </c>
@@ -12955,7 +13001,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="12:71" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L10" t="s">
         <v>496</v>
       </c>
@@ -12981,7 +13027,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="28:67" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AB11" t="s">
         <v>504</v>
       </c>
@@ -12989,11 +13035,11 @@
         <v>505</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:99" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14878,6 +14924,6 @@
     <row r="1898" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>